--- a/results/Int Task Remove ACC -0.3/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_9_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6927028780838842</v>
+        <v>0.6914447823030494</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6923775909618433</v>
+        <v>0.6949986065065744</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.695652924464337</v>
+        <v>0.7022855372021148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6930543712016906</v>
+        <v>0.6993747998153101</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6920878691197697</v>
+        <v>0.7000328614867535</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.692788983498542</v>
+        <v>0.7000328614867535</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.692788983498542</v>
+        <v>0.7013021884086306</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6889941057307937</v>
+        <v>0.7013021884086306</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6825426471383469</v>
+        <v>0.7035660952650341</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6783569672591441</v>
+        <v>0.6974811046451167</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6799628124441043</v>
+        <v>0.6978288540492423</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7290073335191325</v>
+        <v>0.6978120073376788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.725173146757736</v>
+        <v>0.6978120073376788</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7223634896403123</v>
+        <v>0.7020313806400087</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7226831611918321</v>
+        <v>0.6962042902958782</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7249732740440011</v>
+        <v>0.6891247197414341</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7297777066009992</v>
+        <v>0.6971876390893624</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.73299126882776</v>
+        <v>0.6975129262114034</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7258929797049122</v>
+        <v>0.6971895109462029</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7133247089262613</v>
+        <v>0.6920466882692812</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7438114333015811</v>
+        <v>0.6849184494369871</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7466884772652588</v>
+        <v>0.6839818970645125</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7460416467348577</v>
+        <v>0.702665108172527</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7460416467348577</v>
+        <v>0.7000796579077633</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7425383626660234</v>
+        <v>0.7068245820559644</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7113804736213774</v>
+        <v>0.7068245820559644</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6758628220113726</v>
+        <v>0.706822710199124</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6694300819873296</v>
+        <v>0.6958808750306776</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6776273590595792</v>
+        <v>0.6978194947650405</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6873144261926848</v>
+        <v>0.6978194947650405</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6860263807024038</v>
+        <v>0.7074957467252905</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6788326268806961</v>
+        <v>0.7126703909684987</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6852915729005046</v>
+        <v>0.7159139029047059</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6749216939888437</v>
+        <v>0.7103671751184469</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6741255308793983</v>
+        <v>0.7132872717894535</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6719458575808122</v>
+        <v>0.710357815834245</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6575415032258333</v>
+        <v>0.7178600100664301</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6533352329213862</v>
+        <v>0.6903435065286208</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6549466936768675</v>
+        <v>0.6816543470755356</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6100556149465689</v>
+        <v>0.6840006156329164</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.610582646639185</v>
+        <v>0.6840062312034376</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6044527314550983</v>
+        <v>0.6923981813870875</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5920038435460455</v>
+        <v>0.6891565413077207</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6068191744695366</v>
+        <v>0.650299913062649</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5862010873408402</v>
+        <v>0.6553959393185609</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.588347483184486</v>
+        <v>0.6281822606207077</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.588347483184486</v>
+        <v>0.6032306169224178</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.588347483184486</v>
+        <v>0.6113459482618769</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5523454366210072</v>
+        <v>0.6187264717994367</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.524837876399213</v>
+        <v>0.6187208562289156</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5426126129873587</v>
+        <v>0.5954630349870842</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5170370170089391</v>
+        <v>0.5969307787340424</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5038069408451642</v>
+        <v>0.5691230974655058</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.515004804432557</v>
+        <v>0.5726769216690308</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4902051971065253</v>
+        <v>0.6053680694500485</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4911997770410519</v>
+        <v>0.5975593066642264</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4924971818155347</v>
+        <v>0.5811980299746675</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4958525891939785</v>
+        <v>0.5978041039421305</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4958525891939785</v>
+        <v>0.6051116250629152</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4958525891939785</v>
+        <v>0.548132510825572</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4814243166682612</v>
+        <v>0.5394321202314447</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4662911860500909</v>
+        <v>0.5394321202314447</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4419358327475115</v>
+        <v>0.5350241053564223</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4519635778255678</v>
+        <v>0.511397944285221</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.470847077615504</v>
+        <v>0.5184677395872763</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.470847077615504</v>
+        <v>0.5197932222143651</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.464905388035923</v>
+        <v>0.5135903046135032</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4537075244485302</v>
+        <v>0.4985218570483729</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4524138633877282</v>
+        <v>0.5078424562089491</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4645819727707225</v>
+        <v>0.5185058006763643</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4799280791005104</v>
+        <v>0.5249666185530131</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.470954813375873</v>
+        <v>0.5188292159415648</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4900999571552768</v>
+        <v>0.5583719837106859</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4881594655640736</v>
+        <v>0.5297916415352554</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4823810434977933</v>
+        <v>0.5278343032324888</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.486925703922164</v>
+        <v>0.5249254377025245</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.489326256327916</v>
+        <v>0.5252525966814058</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5072282791812082</v>
+        <v>0.5385126225546271</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5043160859057499</v>
+        <v>0.5395465114828017</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5023886973124295</v>
+        <v>0.538580009400881</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4843523167348162</v>
+        <v>0.538580009400881</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4943444965329051</v>
+        <v>0.5508529427669372</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5218530966751663</v>
+        <v>0.5372994513379616</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5286238108509461</v>
+        <v>0.5816391642367191</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4696301626851578</v>
+        <v>0.5865914734841079</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4696301626851578</v>
+        <v>0.5527339509074346</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4683308860538345</v>
+        <v>0.5027108646730698</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.491631760002995</v>
+        <v>0.5055448559294186</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.491631760002995</v>
+        <v>0.4987493916465269</v>
       </c>
     </row>
   </sheetData>
